--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -898,6 +898,386 @@
         <v>1</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1278,6 +1278,346 @@
         <v>2</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1618,6 +1618,326 @@
         <v>1.5</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1938,6 +1938,346 @@
         <v>1.5</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2278,6 +2278,386 @@
         <v>3.25</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1521,12 +1521,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1541,12 +1541,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1561,12 +1561,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1601,12 +1601,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1846,16 +1846,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="73">
@@ -1866,16 +1866,16 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="74">
@@ -1886,16 +1886,16 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="75">
@@ -1906,16 +1906,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="76">
@@ -1926,16 +1926,16 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="77">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2181,101 +2181,101 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2555,106 +2555,6 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
         <v>1</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -866,16 +866,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -886,16 +886,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -906,7 +906,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1241,12 +1241,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1255,18 +1255,18 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="44">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1501,12 +1501,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1806,16 +1806,16 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="71">
@@ -1826,16 +1826,16 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="72">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2141,41 +2141,41 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2515,46 +2515,6 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
         <v>1</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -826,16 +826,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -846,16 +846,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -866,7 +866,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1201,12 +1201,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1215,18 +1215,18 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="42">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1441,12 +1441,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1766,16 +1766,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="69">
@@ -1786,16 +1786,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="70">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2101,41 +2101,41 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2415,106 +2415,6 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
         <v>1</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -786,16 +786,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -806,16 +806,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -826,7 +826,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1161,12 +1161,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1175,18 +1175,18 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="40">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1401,12 +1401,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1421,12 +1421,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1726,16 +1726,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="67">
@@ -1746,16 +1746,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="68">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2061,41 +2061,41 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2375,46 +2375,6 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
         <v>1</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D98"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2278,106 +2278,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2118,166 +2118,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -546,16 +546,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -566,16 +566,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -586,16 +586,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -606,16 +606,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -626,16 +626,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -646,16 +646,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -666,16 +666,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -686,16 +686,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -706,16 +706,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -726,16 +726,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -746,16 +746,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -766,16 +766,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -786,7 +786,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -921,12 +921,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -935,18 +935,18 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -955,18 +955,18 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -975,18 +975,18 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -995,18 +995,18 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1015,18 +1015,18 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1035,18 +1035,18 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1055,18 +1055,18 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1075,18 +1075,18 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1095,18 +1095,18 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1115,18 +1115,18 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1135,18 +1135,18 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1181,7 +1181,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1221,7 +1221,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1301,7 +1301,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1341,12 +1341,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1361,12 +1361,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1381,12 +1381,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1486,16 +1486,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="55">
@@ -1506,16 +1506,16 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="56">
@@ -1526,16 +1526,16 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="57">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="58">
@@ -1566,16 +1566,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="59">
@@ -1586,16 +1586,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="60">
@@ -1606,16 +1606,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="61">
@@ -1626,16 +1626,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="62">
@@ -1646,16 +1646,16 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="63">
@@ -1666,16 +1666,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="64">
@@ -1686,16 +1686,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="65">
@@ -1706,16 +1706,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="66">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1821,300 +1821,60 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
         <v>1</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,16 +446,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -466,16 +466,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -486,16 +486,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -506,16 +506,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -526,16 +526,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -546,7 +546,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -681,12 +681,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -695,18 +695,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -715,18 +715,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -735,18 +735,18 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -755,18 +755,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -775,18 +775,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -795,18 +795,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -815,18 +815,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -835,18 +835,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -855,18 +855,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -875,18 +875,18 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -895,18 +895,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1001,7 +1001,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1061,7 +1061,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1101,12 +1101,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1121,12 +1121,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1141,12 +1141,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1246,16 +1246,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="43">
@@ -1266,16 +1266,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="44">
@@ -1286,16 +1286,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="45">
@@ -1306,16 +1306,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="46">
@@ -1326,16 +1326,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="47">
@@ -1346,16 +1346,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="48">
@@ -1366,16 +1366,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="49">
@@ -1386,16 +1386,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="50">
@@ -1406,16 +1406,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="51">
@@ -1426,16 +1426,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="52">
@@ -1446,16 +1446,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="53">
@@ -1466,16 +1466,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="54">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1581,300 +1581,60 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
         <v>1</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -455,18 +455,18 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -475,18 +475,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -495,18 +495,18 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -515,18 +515,18 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -535,18 +535,18 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -555,18 +555,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -575,18 +575,18 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -595,18 +595,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -615,18 +615,18 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -635,18 +635,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -655,18 +655,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -701,7 +701,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -781,7 +781,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -861,12 +861,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -881,12 +881,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -901,12 +901,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1006,16 +1006,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="31">
@@ -1026,16 +1026,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="32">
@@ -1046,16 +1046,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="33">
@@ -1066,16 +1066,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="34">
@@ -1086,16 +1086,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="35">
@@ -1106,16 +1106,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="36">
@@ -1126,16 +1126,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="37">
@@ -1146,16 +1146,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="38">
@@ -1166,16 +1166,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="39">
@@ -1186,16 +1186,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="40">
@@ -1206,16 +1206,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="41">
@@ -1226,16 +1226,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="42">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1341,300 +1341,60 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
         <v>1</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1338,66 +1338,6 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1338,6 +1338,286 @@
         <v>3.25</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1618,6 +1618,226 @@
         <v>2</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>COCINA Y REPOSTERÍA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>COCINA Y REPOSTERÍA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>COCINA Y REPOSTERÍA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>COCINA Y REPOSTERÍA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>COCINA Y REPOSTERÍA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>COCINA Y REPOSTERÍA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>COCINA Y REPOSTERÍA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>COCINA Y REPOSTERÍA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>COCINA Y REPOSTERÍA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>COCINA Y REPOSTERÍA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>COCINA Y REPOSTERÍA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,6 +1838,406 @@
         <v>2</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2238,6 +2238,406 @@
         <v>1.5</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ARTES PLÁSTICAS</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2638,6 +2638,466 @@
         <v>1.5</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D134"/>
+  <dimension ref="A1:D157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3098,6 +3098,466 @@
         <v>2</v>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D157"/>
+  <dimension ref="A1:D180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3558,6 +3558,466 @@
         <v>1</v>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D180"/>
+  <dimension ref="A1:D203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4018,6 +4018,466 @@
         <v>2.25</v>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D203"/>
+  <dimension ref="A1:D226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4478,6 +4478,466 @@
         <v>2.25</v>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D226"/>
+  <dimension ref="A1:D249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4938,6 +4938,466 @@
         <v>2.25</v>
       </c>
     </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>ARTE Y PINTURA</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D249"/>
+  <dimension ref="A1:D247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -4901,41 +4901,41 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="227">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5355,46 +5355,6 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D248" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D249" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D247"/>
+  <dimension ref="A1:D245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4861,41 +4861,41 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="225">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5315,46 +5315,6 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D246" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D247" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D245"/>
+  <dimension ref="A1:D243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4821,41 +4821,41 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="223">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5275,46 +5275,6 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D244" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D245" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D243"/>
+  <dimension ref="A1:D241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4781,41 +4781,41 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="221">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5235,46 +5235,6 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D242" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D243" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D241"/>
+  <dimension ref="A1:D239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4741,41 +4741,41 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="219">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5195,46 +5195,6 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D240" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D241" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D239"/>
+  <dimension ref="A1:D237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4701,41 +4701,41 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="217">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5155,46 +5155,6 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D238" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D239" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D237"/>
+  <dimension ref="A1:D235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4661,41 +4661,41 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="215">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5115,46 +5115,6 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D236" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D237" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D235"/>
+  <dimension ref="A1:D233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4621,41 +4621,41 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="213">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5075,46 +5075,6 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D234" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D235" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D233"/>
+  <dimension ref="A1:D231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4581,41 +4581,41 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="211">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5035,46 +5035,6 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D232" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D233" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D231"/>
+  <dimension ref="A1:D229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4541,41 +4541,41 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="209">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -4995,46 +4995,6 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D230" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D229"/>
+  <dimension ref="A1:D227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4501,41 +4501,41 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="207">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -4955,46 +4955,6 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D228" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D229" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D227"/>
+  <dimension ref="A1:D225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4461,41 +4461,41 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="205">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4915,46 +4915,6 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D227" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D225"/>
+  <dimension ref="A1:D223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4421,41 +4421,41 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="203">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4875,46 +4875,6 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D223"/>
+  <dimension ref="A1:D221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4381,41 +4381,41 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="201">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4835,46 +4835,6 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D221"/>
+  <dimension ref="A1:D219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4341,41 +4341,41 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="199">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4795,46 +4795,6 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D219"/>
+  <dimension ref="A1:D217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4301,41 +4301,41 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="197">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4755,46 +4755,6 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D217"/>
+  <dimension ref="A1:D215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4261,41 +4261,41 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="195">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4715,46 +4715,6 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D215"/>
+  <dimension ref="A1:D213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4221,41 +4221,41 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="193">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4675,46 +4675,6 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D213"/>
+  <dimension ref="A1:D211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4181,41 +4181,41 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="191">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4635,46 +4635,6 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D211"/>
+  <dimension ref="A1:D209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4141,41 +4141,41 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="189">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4595,46 +4595,6 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D210" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D211" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D209"/>
+  <dimension ref="A1:D207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4101,41 +4101,41 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="187">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4555,46 +4555,6 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D208" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D209" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D207"/>
+  <dimension ref="A1:D205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4061,41 +4061,41 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="185">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4515,46 +4515,6 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D206" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D207" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D205"/>
+  <dimension ref="A1:D203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4021,41 +4021,41 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="183">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4475,46 +4475,6 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D204" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D205" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D203"/>
+  <dimension ref="A1:D201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3981,41 +3981,41 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="181">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4435,46 +4435,6 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D203" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D201"/>
+  <dimension ref="A1:D199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3941,41 +3941,41 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="179">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4395,46 +4395,6 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D199"/>
+  <dimension ref="A1:D197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3901,41 +3901,41 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="177">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4355,46 +4355,6 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D197"/>
+  <dimension ref="A1:D195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3861,41 +3861,41 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="175">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4315,46 +4315,6 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D195"/>
+  <dimension ref="A1:D193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3821,41 +3821,41 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="173">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4275,46 +4275,6 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3781,41 +3781,41 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="171">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4235,46 +4235,6 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D191"/>
+  <dimension ref="A1:D189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3741,41 +3741,41 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="169">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4195,46 +4195,6 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D189"/>
+  <dimension ref="A1:D187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3701,41 +3701,41 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="167">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4155,46 +4155,6 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D187"/>
+  <dimension ref="A1:D185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3661,41 +3661,41 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="165">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4115,46 +4115,6 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D185"/>
+  <dimension ref="A1:D183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3621,41 +3621,41 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="163">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4075,46 +4075,6 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D183"/>
+  <dimension ref="A1:D181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3581,41 +3581,41 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="161">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4035,46 +4035,6 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D181"/>
+  <dimension ref="A1:D180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3561,21 +3561,21 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>AUTONOMÍA Y VIDA INDEPENDIENTE</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="159">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4015,26 +4015,6 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D180"/>
+  <dimension ref="A1:D179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -3995,26 +3995,6 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D179"/>
+  <dimension ref="A1:D178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3975,26 +3975,6 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D178"/>
+  <dimension ref="A1:D177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3955,26 +3955,6 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D177"/>
+  <dimension ref="A1:D176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3935,26 +3935,6 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D176"/>
+  <dimension ref="A1:D175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3915,26 +3915,6 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D175"/>
+  <dimension ref="A1:D174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3895,26 +3895,6 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D174"/>
+  <dimension ref="A1:D173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3875,26 +3875,6 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D173"/>
+  <dimension ref="A1:D172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3855,26 +3855,6 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D172"/>
+  <dimension ref="A1:D171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3835,26 +3835,6 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D171"/>
+  <dimension ref="A1:D170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3815,26 +3815,6 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D170"/>
+  <dimension ref="A1:D169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3795,26 +3795,6 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D169"/>
+  <dimension ref="A1:D168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3775,26 +3775,6 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D168"/>
+  <dimension ref="A1:D167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3755,26 +3755,6 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D167"/>
+  <dimension ref="A1:D166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3735,26 +3735,6 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D166"/>
+  <dimension ref="A1:D165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3715,26 +3715,6 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D165"/>
+  <dimension ref="A1:D164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3695,26 +3695,6 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D164"/>
+  <dimension ref="A1:D163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3675,26 +3675,6 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D163"/>
+  <dimension ref="A1:D162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3655,26 +3655,6 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D162"/>
+  <dimension ref="A1:D161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3635,26 +3635,6 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3615,26 +3615,6 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D160"/>
+  <dimension ref="A1:D159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3595,26 +3595,6 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D159"/>
+  <dimension ref="A1:D157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3558,46 +3558,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>ARTE Y PINTURA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D157"/>
+  <dimension ref="A1:D163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3558,6 +3558,126 @@
         <v>1</v>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D163"/>
+  <dimension ref="A1:D180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3678,6 +3678,346 @@
         <v>1</v>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D180"/>
+  <dimension ref="A1:D191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4018,6 +4018,226 @@
         <v>2.25</v>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (nan)</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (nan)</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (nan)</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (nan)</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (nan)</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (nan)</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (nan)</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (nan)</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (nan)</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (nan)</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (nan)</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D191"/>
+  <dimension ref="A1:D174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3561,7 +3561,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3575,18 +3575,18 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3595,18 +3595,18 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3615,18 +3615,18 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3635,18 +3635,18 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3655,18 +3655,18 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="164">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3896,346 +3896,6 @@
       </c>
       <c r="D174" t="n">
         <v>2.25</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO (nan)</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO (nan)</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO (nan)</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO (nan)</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO (nan)</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO (nan)</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO (nan)</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO (nan)</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO (nan)</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO (nan)</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO (nan)</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D174"/>
+  <dimension ref="A1:D168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3775,126 +3775,6 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
         <v>2.25</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D168"/>
+  <dimension ref="A1:D162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3655,126 +3655,6 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
         <v>2.25</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D162"/>
+  <dimension ref="A1:D157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3558,106 +3558,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>GRUPO DE CRECIMIENTO</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D157"/>
+  <dimension ref="A1:D147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1641,201 +1641,201 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>COCINA Y REPOSTERÍA</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>COCINA Y REPOSTERÍA</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>COCINA Y REPOSTERÍA</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>COCINA Y REPOSTERÍA</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>COCINA Y REPOSTERÍA</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>COCINA Y REPOSTERÍA</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>COCINA Y REPOSTERÍA</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>COCINA Y REPOSTERÍA</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>COCINA Y REPOSTERÍA</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>COCINA Y REPOSTERÍA</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="72">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2441,201 +2441,201 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2901,201 +2901,201 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3355,206 +3355,6 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
         <v>1</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D147"/>
+  <dimension ref="A1:D146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1621,21 +1621,21 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>COCINA Y REPOSTERÍA</t>
+          <t>ARTES PLÁSTICAS</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="62">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2421,21 +2421,21 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ARTE Y PINTURA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2881,21 +2881,21 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>CONVIVENCIA INSTITUCIONAL</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3335,26 +3335,6 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
         <v>1</v>
       </c>
     </row>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D146"/>
+  <dimension ref="A1:D153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3338,6 +3338,146 @@
         <v>1</v>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D153"/>
+  <dimension ref="A1:D160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3478,6 +3478,146 @@
         <v>2</v>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D160"/>
+  <dimension ref="A1:D426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,17 +441,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -461,17 +461,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -481,17 +481,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -501,17 +501,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -521,17 +521,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -541,17 +541,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -561,17 +561,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -581,17 +581,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -601,17 +601,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -621,17 +621,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -641,17 +641,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -661,17 +661,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -681,17 +681,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -701,17 +701,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -721,17 +721,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -741,17 +741,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -761,17 +761,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TEATRO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -781,17 +781,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TEATRO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -801,17 +801,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TEATRO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -821,17 +821,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TEATRO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -841,17 +841,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TEATRO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -861,17 +861,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TEATRO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -881,17 +881,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TEATRO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -901,17 +901,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TEATRO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -921,17 +921,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>OTRA (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -941,17 +941,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>OTRA (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -961,17 +961,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>OTRA (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -981,17 +981,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>OTRA (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1001,227 +1001,227 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>OTRA (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>OTRA (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>OTRA (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>MOVIMIENTO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>MOVIMIENTO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>MOVIMIENTO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>MOVIMIENTO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>MOVIMIENTO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>MOVIMIENTO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>TEATRO (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>TEATRO (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1231,37 +1231,37 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>TEATRO (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>TEATRO (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1271,367 +1271,367 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>TEATRO (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>FELDENKRAIS (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>FELDENKRAIS (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>FELDENKRAIS (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>MOVIMIENTO VITAL EXPRESIVO (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>MOVIMIENTO VITAL EXPRESIVO (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>MOVIMIENTO VITAL EXPRESIVO (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>MOVIMIENTO VITAL EXPRESIVO (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>MOVIMIENTO VITAL EXPRESIVO (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>MOVIMIENTO VITAL EXPRESIVO (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>MOVIMIENTO VITAL EXPRESIVO (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>MOVIMIENTO VITAL EXPRESIVO (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>MOVIMIENTO VITAL EXPRESIVO (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>MOVIMIENTO VITAL EXPRESIVO (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -1641,17 +1641,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -1661,17 +1661,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -1681,17 +1681,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -1701,17 +1701,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -1721,17 +1721,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -1741,17 +1741,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -1761,7 +1761,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -1781,17 +1781,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TEATRO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -1801,17 +1801,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TEATRO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -1821,17 +1821,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TEATRO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -1841,7 +1841,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TEATRO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -1861,17 +1861,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TEATRO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -1881,17 +1881,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>DESARROLLO EDUCATIVO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -1901,17 +1901,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>DESARROLLO EDUCATIVO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -1921,17 +1921,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>DESARROLLO EDUCATIVO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -1941,17 +1941,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>DESARROLLO EDUCATIVO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -1961,17 +1961,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>DESARROLLO EDUCATIVO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -1981,17 +1981,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>DESARROLLO EDUCATIVO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -2001,7 +2001,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>DESARROLLO EDUCATIVO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -2021,17 +2021,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>DESARROLLO EDUCATIVO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -2041,17 +2041,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>DESARROLLO EDUCATIVO (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -2061,17 +2061,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER "SÍ PUEDO" (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -2081,17 +2081,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER "SÍ PUEDO" (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -2101,17 +2101,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER "SÍ PUEDO" (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -2121,17 +2121,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER "SÍ PUEDO" (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -2141,17 +2141,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER "SÍ PUEDO" (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -2161,17 +2161,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER "SÍ PUEDO" (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -2181,17 +2181,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER "SÍ PUEDO" (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -2201,17 +2201,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER "SÍ PUEDO" (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -2221,17 +2221,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER "SÍ PUEDO" (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -2241,17 +2241,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -2261,17 +2261,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -2281,17 +2281,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -2301,17 +2301,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -2321,17 +2321,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -2341,17 +2341,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -2361,17 +2361,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>TALLER DE COMUNICACIÓN (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -2381,17 +2381,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -2401,17 +2401,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ARTES PLÁSTICAS</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -2421,1201 +2421,6521 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>OTRA (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>OTRA (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>OTRA (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>OTRA (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>OTRA (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>MOVIMIENTO VITAL EXPRESIVO (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>MOVIMIENTO VITAL EXPRESIVO (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>MOVIMIENTO VITAL EXPRESIVO (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>MOVIMIENTO VITAL EXPRESIVO (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>MOVIMIENTO VITAL EXPRESIVO (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>MOVIMIENTO VITAL EXPRESIVO (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ARTE Y PINTURA</t>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EFRAÍN MAYNEZ PORRAS</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>FERNANDO ÁVILA BERLANGA</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>GUADALUPE LÓPEZ TOVAR</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>JESÚS SALCIDO ZAMORA</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+          <t>JESÚS SALCIDO ZAMORA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CONVIVENCIA INSTITUCIONAL</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+          <t>AJEDREZ (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+          <t>AJEDREZ (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+          <t>AJEDREZ (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+          <t>AJEDREZ (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+          <t>AJEDREZ (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
+          <t>AJEDREZ (09:00 - 10:30)</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>AJEDREZ (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>OTRA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>OTRA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
           <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>TALLER "SÍ PUEDO" (10:00 - 12:00)</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>2</v>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>OTRA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>OTRA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>OTRA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>OTRA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>OTRA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>OTRA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>OTRA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>TEATRO (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>TEATRO (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>TEATRO (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>TEATRO (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>TEATRO (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>TEATRO (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>TEATRO (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>TEATRO (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>TEATRO (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>TEATRO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>TEATRO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>TEATRO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>TEATRO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>TEATRO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>TEATRO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>TEATRO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>TEATRO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>TEATRO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>TEATRO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ARTE (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>ARTE (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>ARTE (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ARTE (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>ARTE (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>ARTE (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>ARTE (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>ARTE (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>TEATRO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>TEATRO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>TEATRO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>TEATRO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>TEATRO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>TEATRO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>TEATRO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>27/06/2026</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>TEATRO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>TEATRO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>TEATRO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>TEATRO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>TEATRO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO VITAL EXPRESIVO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO VITAL EXPRESIVO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO VITAL EXPRESIVO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO VITAL EXPRESIVO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO VITAL EXPRESIVO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>OTRA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>OTRA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>OTRA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>OTRA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>OTRA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>TALLER DE COMUNICACIÓN (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO VITAL EXPRESIVO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO VITAL EXPRESIVO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO VITAL EXPRESIVO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO VITAL EXPRESIVO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO VITAL EXPRESIVO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO VITAL EXPRESIVO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>ARTE (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>ARTE (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>ARTE (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>ARTE (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>ARTE (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>ARTE (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>ARTE (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO VITAL EXPRESIVO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO VITAL EXPRESIVO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO VITAL EXPRESIVO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO VITAL EXPRESIVO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>GRUPO DE CRECIMIENTO (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>FELDENKRAIS (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>FELDENKRAIS (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>FELDENKRAIS (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D359" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>FELDENKRAIS (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D360" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>FELDENKRAIS (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D361" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>FELDENKRAIS (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>FELDENKRAIS (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D363" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>FELDENKRAIS (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D364" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>FELDENKRAIS (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D365" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D366" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D367" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D368" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D369" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D370" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D371" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>TALLER "SÍ PUEDO" (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D372" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D373" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D374" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D375" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D376" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>EFRAÍN MAYNEZ PORRAS</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D377" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D378" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D379" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D380" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>JESÚS ALEJANDRO SIFUENTES ESPINO</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D381" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D382" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D383" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D384" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D385" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (11:00 - 12:30)</t>
+        </is>
+      </c>
+      <c r="D386" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D387" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D388" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D389" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D390" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FUERA DE COMUNIDAD (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D392" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>JUAN RAFAEL YAÑEZ SERNA</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>MOVIMIENTO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DE LA TORRE SANTELLANO</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>TEATRO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>TEATRO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>TEATRO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>FLORINDA ESTEVANÉ PIZARRO</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>TEATRO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>MARÍA DE LOS ÁNGELES ORDUÑA RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>TEATRO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>TEATRO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>TOMASITA MARÍA ENRIQUETA RIVERA DEL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>TEATRO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D409" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>TEATRO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D410" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>GUADALUPE LÓPEZ TOVAR</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>TEATRO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D411" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>TEATRO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D412" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>TEATRO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D413" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>TEATRO (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D414" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D415" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D416" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D417" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO DE LA CERDA TREVIÑO</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D418" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>TERESITA DEL NIÑO JESÚS RODRÍGUEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>VIDA DIARIA (13:00 - 14:30)</t>
+        </is>
+      </c>
+      <c r="D419" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>JUAN SILVERIO LÓPEZ DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D420" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>ANA DE LOS ÁNGELES TORRES REVELES</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D421" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>JUAN JOSÉ OCHOA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>JOSE REYNALDO ALCORTA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER GARCÍA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>CRISTABEL DE LA CRUZ MALDONADO</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>MA. ELIZABETH GONZÁLEZ HIDROGO</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>PSICOLOGÍA (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/asistencia.xlsx
+++ b/asistencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D426"/>
+  <dimension ref="A1:D431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8938,6 +8938,106 @@
         <v>1.5</v>
       </c>
     </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>FERNANDO ÁVILA BERLANGA</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>MARÍA GUADALUPE DE LA CONCEPCIÓN TORRES LIRA</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>KARLA LISSETTE PEDROZA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>ISAAC IGNACIO GONZÁLEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D430" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>JESÚS SALCIDO ZAMORA</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>DESARROLLO EDUCATIVO (09:00 - 10:30)</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
